--- a/data/trans_bre/P6905-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 12,96</t>
+          <t>-20,95; 12,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 30,09</t>
+          <t>-5,44; 30,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 50,09</t>
+          <t>-1,79; 48,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,72; 65,55</t>
+          <t>9,71; 66,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 57,7</t>
+          <t>-68,25; 54,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 296,97</t>
+          <t>-26,51; 288,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 380,01</t>
+          <t>-8,42; 379,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,08; 7532,28</t>
+          <t>-43,12; 8545,21</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 29,34</t>
+          <t>6,69; 29,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 24,67</t>
+          <t>2,86; 24,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 28,87</t>
+          <t>7,52; 28,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 15,4</t>
+          <t>-6,78; 15,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,07; 117,94</t>
+          <t>20,66; 110,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 101,11</t>
+          <t>8,27; 102,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,96; 126,76</t>
+          <t>24,73; 128,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 88,92</t>
+          <t>-22,19; 89,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 20,22</t>
+          <t>-14,42; 20,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 40,71</t>
+          <t>-0,36; 39,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 19,47</t>
+          <t>-14,31; 19,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 22,43</t>
+          <t>-11,05; 21,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 79,26</t>
+          <t>-33,33; 69,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 278,15</t>
+          <t>-1,43; 253,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 75,32</t>
+          <t>-33,73; 78,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 93,73</t>
+          <t>-24,43; 83,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,85</t>
+          <t>3,01; 18,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 23,49</t>
+          <t>6,77; 23,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 22,68</t>
+          <t>5,97; 23,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 16,83</t>
+          <t>-0,79; 17,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 70,17</t>
+          <t>8,28; 67,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,32; 102,74</t>
+          <t>20,98; 103,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,72; 94,18</t>
+          <t>20,17; 102,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 87,4</t>
+          <t>-0,31; 86,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6905-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35,31</t>
+          <t>16,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>371,4%</t>
+          <t>126,62%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 12,3</t>
+          <t>-20,8; 12,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 30,5</t>
+          <t>-5,31; 30,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 48,42</t>
+          <t>-2,48; 49,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 66,41</t>
+          <t>-3,36; 36,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,25; 54,61</t>
+          <t>-65,28; 55,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 288,49</t>
+          <t>-24,3; 297,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 379,56</t>
+          <t>-12,38; 386,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 8545,21</t>
+          <t>-25,87; 1199,55</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>8,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 29,02</t>
+          <t>7,12; 29,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 24,74</t>
+          <t>2,48; 24,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 28,78</t>
+          <t>6,98; 27,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 15,19</t>
+          <t>0,58; 16,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,66; 110,63</t>
+          <t>21,95; 114,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 102,07</t>
+          <t>7,24; 103,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,73; 128,04</t>
+          <t>22,61; 128,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 89,9</t>
+          <t>1,17; 87,1</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>-0,73</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>-1,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 20,79</t>
+          <t>-12,82; 22,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 39,81</t>
+          <t>1,69; 40,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 19,44</t>
+          <t>-15,55; 20,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 21,49</t>
+          <t>-18,41; 15,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 69,01</t>
+          <t>-31,32; 80,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 253,58</t>
+          <t>2,62; 268,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 78,11</t>
+          <t>-36,52; 78,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 83,6</t>
+          <t>-34,92; 51,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,39</t>
+          <t>8,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 18,75</t>
+          <t>2,9; 19,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 23,55</t>
+          <t>7,03; 23,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 23,49</t>
+          <t>6,64; 23,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 17,12</t>
+          <t>1,98; 15,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 67,27</t>
+          <t>8,99; 71,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,98; 103,2</t>
+          <t>23,75; 103,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,17; 102,69</t>
+          <t>22,06; 97,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 86,99</t>
+          <t>4,57; 70,71</t>
         </is>
       </c>
     </row>
